--- a/4_pagos/yape/motor_matching/trazabilidad/trazabilidad_2026_08.xlsx
+++ b/4_pagos/yape/motor_matching/trazabilidad/trazabilidad_2026_08.xlsx
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="Q3" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="Q4" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q5" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="Q6" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,109 @@
       </c>
       <c r="Q7" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>U0368</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>NELY MORENO LICITA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>JAVIER VEN*</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>08/08/2026 18:40:34</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>17/08/2026 20:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>JAVIER VEN*</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>08/08/2026 18:38:28</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1358,7 @@
       </c>
       <c r="Q3" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1425,7 @@
       </c>
       <c r="Q4" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1606,7 @@
       </c>
       <c r="P3" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1654,7 @@
       </c>
       <c r="P4" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1702,7 @@
       </c>
       <c r="P5" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1750,7 @@
       </c>
       <c r="P6" s="18" t="inlineStr">
         <is>
-          <t>12/08/2026 08:24</t>
+          <t>17/08/2026 20:23</t>
         </is>
       </c>
     </row>
